--- a/hairdresser_forms/011_hair_texture_relaxation_service_consent_form--hairdresser_forms.xlsx
+++ b/hairdresser_forms/011_hair_texture_relaxation_service_consent_form--hairdresser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'high_risk_of_burns_or_scarring'}</t>
+          <t>high_risk_of_burns_or_scarring</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'High risk of burns or scarring'}</t>
+          <t>High risk of burns or scarring</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'high_risk_of_hair_breakage'}</t>
+          <t>high_risk_of_hair_breakage</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'High risk of hair breakage'}</t>
+          <t>High risk of hair breakage</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'skin_irritation'}</t>
+          <t>skin_irritation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Skin irritation'}</t>
+          <t>Skin irritation</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'client_has_read_and_signed_this_form'}</t>
+          <t>client_has_read_and_signed_this_form</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Client has read and signed this form'}</t>
+          <t>Client has read and signed this form</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'client_has_read_and_signed_this_form'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Client has read and signed this form'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'chemical_relaxing'}</t>
+          <t>chemical_relaxing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Chemical Relaxing'}</t>
+          <t>Chemical Relaxing</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'haircut'}</t>
+          <t>haircut</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Haircut'}</t>
+          <t>Haircut</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'chemical_treatment'}</t>
+          <t>chemical_treatment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Chemical Treatment'}</t>
+          <t>Chemical Treatment</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'i_have_read_and_understand_the_risks_associated_with_this_service'}</t>
+          <t>i_have_read_and_understand_the_risks_associated_with_this_service</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'I have read and understand the risks associated with this service'}</t>
+          <t>I have read and understand the risks associated with this service</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'i_have_read_and_understand_the_risks_associated_with_this_service'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'I have read and understand the risks associated with this service'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
